--- a/vsong/minato/static/minato/assets/bookmarks/bookmarks.xlsx
+++ b/vsong/minato/static/minato/assets/bookmarks/bookmarks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>FUN</t>
   </si>
@@ -25,18 +25,116 @@
   </si>
   <si>
     <t>https://pbfcomics.com/</t>
+  </si>
+  <si>
+    <t>XKCD</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Kingdom</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Phylum</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Workbook</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Worksheet</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Genus</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Address</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Eukarya.Animalia.Chordata.Mammalia.Carnivora.Felidae.Felis.FelixCatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">universal Turing machine (UTM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitedStates.CA.LA.WestHollyWood.123Home Street</t>
+  </si>
+  <si>
+    <t>Class("Mammalia").Order("Carnivora").Family("Felidae").Genus("Felis").Species("FelisCatus")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -59,8 +157,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.140625"/>
+    <col customWidth="1" min="1" max="1" width="15.421875"/>
+    <col customWidth="1" min="2" max="2" width="16.00390625"/>
+    <col customWidth="1" min="3" max="3" width="11.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -572,6 +675,155 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="15">
+      <c r="B28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="B34" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
